--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,29 +617,29 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -671,27 +671,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -713,27 +713,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -755,27 +755,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -797,27 +797,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -839,27 +839,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -965,40 +965,82 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,39 +617,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,29 +659,29 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -713,27 +713,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -755,27 +755,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -797,27 +797,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -839,27 +839,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -965,27 +965,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1007,40 +1007,82 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,39 +617,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,29 +701,29 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -755,27 +755,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -797,27 +797,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -839,27 +839,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -965,27 +965,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1007,27 +1007,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1049,40 +1049,82 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,39 +617,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -839,27 +839,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -965,27 +965,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1007,27 +1007,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1049,27 +1049,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1091,40 +1091,124 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>혁신행정감사담당관실</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,29 +491,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -545,27 +545,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,34 +575,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -617,39 +617,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,29 +827,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -965,27 +965,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1007,27 +1007,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1049,27 +1049,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1133,27 +1133,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1175,40 +1175,82 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,29 +533,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -587,27 +587,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,34 +617,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,39 +827,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,29 +869,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -965,27 +965,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1007,27 +1007,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1049,27 +1049,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1133,27 +1133,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1175,27 +1175,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1217,40 +1217,82 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,29 +575,29 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -629,27 +629,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,34 +659,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,39 +827,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,39 +869,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -911,29 +911,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -965,27 +965,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1007,27 +1007,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1049,27 +1049,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1133,27 +1133,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1175,27 +1175,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1259,40 +1259,82 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,29 +617,29 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -671,27 +671,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,34 +701,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,39 +827,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,39 +869,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -911,39 +911,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -953,29 +953,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1007,27 +1007,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1049,27 +1049,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1133,27 +1133,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1175,27 +1175,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1259,27 +1259,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1301,40 +1301,82 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,39 +617,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,39 +827,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,39 +869,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -911,39 +911,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -953,39 +953,39 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -995,39 +995,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1037,39 +1037,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1133,27 +1133,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1175,27 +1175,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1259,27 +1259,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1301,27 +1301,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1343,40 +1343,124 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>혁신행정감사담당관실</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
+          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,29 +491,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -545,27 +545,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,34 +575,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -617,39 +617,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,29 +743,29 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -797,27 +797,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,34 +827,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -869,39 +869,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -911,39 +911,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -953,39 +953,39 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -995,39 +995,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1037,39 +1037,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1079,29 +1079,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1133,27 +1133,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1175,27 +1175,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1259,27 +1259,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1301,27 +1301,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1343,27 +1343,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1385,27 +1385,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1427,40 +1427,82 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
+          <t>법제처, 제3회 특별성과 포상 수여</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
+          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,29 +533,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -587,27 +587,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,34 +617,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,29 +785,29 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -839,27 +839,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,34 +869,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -911,39 +911,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -953,39 +953,39 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -995,39 +995,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1037,39 +1037,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1079,39 +1079,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1121,29 +1121,29 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1175,27 +1175,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1259,27 +1259,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1301,27 +1301,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1343,27 +1343,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1385,27 +1385,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1427,27 +1427,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1469,40 +1469,82 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>법제처, 제3회 특별성과 포상 수여</t>
+          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
+          <t>법제처, 제3회 특별성과 포상 수여</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
+          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,29 +575,29 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -629,27 +629,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,34 +659,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -701,39 +701,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,29 +827,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -911,34 +911,34 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -953,39 +953,39 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -995,39 +995,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1037,39 +1037,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1079,39 +1079,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1121,39 +1121,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1163,29 +1163,29 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1259,27 +1259,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1301,27 +1301,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1343,27 +1343,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1385,27 +1385,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1427,27 +1427,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1469,27 +1469,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1511,40 +1511,82 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/moleg_news.xlsx
+++ b/docs/snapshot/downloads/moleg_news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
+          <t>법제처, 추석맞이 아동양육시설 봉사활동, 따뜻한 나눔 실천</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>법제처, 제3회 특별성과 포상 수여</t>
+          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
+          <t>법제처, 제3회 특별성과 포상 수여</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
+          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,29 +617,29 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -671,27 +671,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -701,34 +701,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -743,39 +743,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,39 +827,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,29 +869,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -953,34 +953,34 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -995,39 +995,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1037,39 +1037,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1079,39 +1079,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1121,39 +1121,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1163,39 +1163,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1205,29 +1205,29 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1259,27 +1259,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1301,27 +1301,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1343,27 +1343,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1385,27 +1385,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1427,27 +1427,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1469,27 +1469,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1511,27 +1511,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1553,40 +1553,82 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>
